--- a/output/laminas_comunales/comunal_o_ocup_a_2021_aysen.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2021_aysen.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,136 +375,1156 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11101</t>
+          <t>11302</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Coyhaique</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="C2">
-        <v>38.1146751192802</v>
+        <v>55.9851089578675</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11101</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Coyhaique</t>
         </is>
       </c>
       <c r="C3">
-        <v>36.9692346809052</v>
+        <v>55.1361692550079</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>11201</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cisnes</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="C4">
-        <v>33.1459610871376</v>
+        <v>54.3967197141929</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11102</t>
+          <t>11201</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lago Verde</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="C5">
-        <v>31.2346588119784</v>
+        <v>53.208944576313</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11301</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cochrane</t>
+          <t>Cisnes</t>
         </is>
       </c>
       <c r="C6">
-        <v>29.1079023953436</v>
+        <v>50.1856118791603</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11401</t>
+          <t>11101</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chile Chico</t>
+          <t>Coyhaique</t>
         </is>
       </c>
       <c r="C7">
-        <v>28.4611406619385</v>
+        <v>47.3546453259903</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11203</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Guaitecas</t>
+          <t>Lago Verde</t>
         </is>
       </c>
       <c r="C8">
-        <v>27.8523035230352</v>
+        <v>47.0170454545455</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>11402</t>
+          <t>11302</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Río Ibáñez</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="C9">
-        <v>24.5896184560781</v>
+        <v>46.9010050841721</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>11301</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Cochrane</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>45.4967766401214</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>11401</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Chile Chico</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>44.7907949790795</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>44.5866942818611</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>43.8248678310915</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>43.7827203850031</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>11402</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Río Ibáñez</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>42.5862068965517</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>40.9830367074527</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>11203</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Guaitecas</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>40.6593406593407</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>11102</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Lago Verde</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>40.5448717948718</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>11101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Coyhaique</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>39.1842186514169</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>11101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Coyhaique</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>38.1146751192802</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>38.0903590944575</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>37.6853520803482</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cisnes</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>37.5493204734765</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>11101</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Coyhaique</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>37.066242943429</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>36.9692346809052</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>36.2032329849383</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Cisnes</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>35.2335164835165</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>34.9041802906116</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>34.2775569291574</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>11401</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Chile Chico</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>34.2655642023346</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>11102</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Lago Verde</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>33.5726718885988</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Cisnes</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>33.1459610871376</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>32.7190485538542</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>11303</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Tortel</t>
         </is>
       </c>
-      <c r="C10">
+      <c r="C34">
+        <v>31.9298245614035</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>11301</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Cochrane</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>31.9102564102564</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>31.2656095719347</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>11102</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Lago Verde</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>31.2346588119784</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>30.8198372899844</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>11101</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Coyhaique</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>30.7269152807287</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>11401</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Chile Chico</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>30.3113941967445</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>30.2021945333109</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>11301</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Cochrane</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>30.0312283136711</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>11303</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Tortel</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>29.2955326460481</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>11301</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Cochrane</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>29.1079023953436</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Cisnes</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>28.9108494533221</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>11401</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Chile Chico</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>28.4611406619385</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Cisnes</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>28.4126610116243</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>11301</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Cochrane</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>28.2422468011277</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>11203</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Guaitecas</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>28.2107413893754</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>11102</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Lago Verde</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>28.2094594594595</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>11203</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Guaitecas</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>27.8523035230352</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>11203</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Guaitecas</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>27.5417298937785</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>11402</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Río Ibáñez</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>27.4173027989822</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>11401</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Chile Chico</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>27.2904940587867</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>11102</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Lago Verde</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>26.7429193899782</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>11203</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Guaitecas</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>26.6666666666667</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>11402</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Río Ibáñez</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>26.480372588157</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>11401</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Chile Chico</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>26.4410446607943</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>11203</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Guaitecas</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>26.3738738738739</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>11301</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Cochrane</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>25.831255195345</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>11402</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Río Ibáñez</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>25.6280637254902</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>11303</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Tortel</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>25.354609929078</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>11402</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Río Ibáñez</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>24.5896184560781</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>11303</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Tortel</t>
+        </is>
+      </c>
+      <c r="C64">
         <v>22.7128623188406</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>11402</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Río Ibáñez</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>21.4883720930233</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>11303</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Tortel</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>19.9537037037037</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>11303</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Tortel</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>11102</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Lago Verde</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>12.9725085910653</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>11101</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Coyhaique</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>12.4619784434305</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>11.1690780931182</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>11302</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>11.0684816500625</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>11201</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>10.4359850333496</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>11202</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Cisnes</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>9.45121951219512</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>11203</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Guaitecas</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>8.6734693877551</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>11401</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Chile Chico</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>8.64677023712183</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>11301</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Cochrane</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>8.08861411643483</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>11303</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Tortel</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>7.02614379084967</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>11402</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Río Ibáñez</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>5.59088500264971</v>
       </c>
     </row>
   </sheetData>
